--- a/sales_analysis.xlsx
+++ b/sales_analysis.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30023"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E72FF089-526C-4853-B325-4520BB0E5219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{65B12ADC-2742-405D-B8AA-D6EF4C2EA806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw Data" sheetId="1" r:id="rId1"/>
@@ -26,9 +26,6 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
@@ -206,11 +203,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -321,7 +317,7 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ar-SA"/>
-  <c:roundedCorners val="0"/>
+  <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
     <c:title>
@@ -355,6 +351,7 @@
         <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </c:spPr>
     </c:title>
@@ -387,6 +384,7 @@
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
+              <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
@@ -395,11 +393,11 @@
               <a:noFill/>
               <a:ln>
                 <a:noFill/>
+                <a:prstDash val="solid"/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -416,11 +414,10 @@
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="1"/>
-            <c:separator> </c:separator>
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
+                <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
@@ -479,7 +476,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-DF94-4703-BAA2-DB02F9E084E6}"/>
+              <c16:uniqueId val="{00000000-90D9-468C-B9F4-ED065582C4FF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -533,6 +530,7 @@
             <a:noFill/>
             <a:ln w="0">
               <a:noFill/>
+              <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
         </c:title>
@@ -545,6 +543,7 @@
             <a:solidFill>
               <a:srgbClr val="B3B3B3"/>
             </a:solidFill>
+            <a:prstDash val="solid"/>
           </a:ln>
         </c:spPr>
         <c:txPr>
@@ -582,6 +581,7 @@
               <a:solidFill>
                 <a:srgbClr val="B3B3B3"/>
               </a:solidFill>
+              <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
@@ -616,6 +616,7 @@
             <a:noFill/>
             <a:ln w="0">
               <a:noFill/>
+              <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
         </c:title>
@@ -628,6 +629,7 @@
             <a:solidFill>
               <a:srgbClr val="B3B3B3"/>
             </a:solidFill>
+            <a:prstDash val="solid"/>
           </a:ln>
         </c:spPr>
         <c:txPr>
@@ -649,12 +651,6 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
@@ -663,6 +659,7 @@
         <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </c:spPr>
       <c:txPr>
@@ -693,6 +690,7 @@
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
+      <a:prstDash val="solid"/>
       <a:round/>
     </a:ln>
   </c:spPr>
@@ -939,407 +937,439 @@
   <dimension ref="A1:J24"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="14.375" customWidth="1"/>
-    <col min="5" max="5" width="16.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.75" customWidth="1"/>
-    <col min="8" max="8" width="8.25" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="36" customWidth="1"/>
+    <col min="2" max="2" width="11.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="16.75" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13" style="1" customWidth="1"/>
+    <col min="10" max="10" width="36" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>30</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>800</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="2">
         <v>24000</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="5"/>
+      <c r="G2" s="1"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="4"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>50</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>400</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="2">
         <v>20000</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="6"/>
+      <c r="G3" s="1"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="5"/>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>80</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>100</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="2">
         <v>8000</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
+      <c r="G4" s="1"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>25</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>800</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="2">
         <v>20000</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="G5" s="1"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>60</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>400</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="2">
         <v>24000</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="G6" s="1"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>90</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>100</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="2">
         <v>9000</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="G7" s="1"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" t="s">
+      <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>40</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>800</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="2">
         <v>32000</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" t="s">
+      <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>70</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>400</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="2">
         <v>28000</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="G9" s="1"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" t="s">
+      <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>60</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>100</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="2">
         <v>6000</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="G10" s="1"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" t="s">
+      <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>20</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>800</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="2">
         <v>16000</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="G11" s="1"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" t="s">
+      <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <v>55</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="1">
         <v>400</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="2">
         <v>22000</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" t="s">
+      <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>100</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>100</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="2">
         <v>10000</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="G13" s="1"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" t="s">
+      <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="1">
         <v>35</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <v>800</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="2">
         <v>28000</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" t="s">
+      <c r="A15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <v>65</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <v>400</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="2">
         <v>26000</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" t="s">
+      <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="1">
         <v>75</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="1">
         <v>100</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" s="2">
         <v>7500</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="G16" s="1"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" t="s">
+      <c r="A17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="1">
         <v>45</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="1">
         <v>800</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" s="2">
         <v>36000</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="G17" s="1"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" t="s">
+      <c r="A18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="1">
         <v>80</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="1">
         <v>400</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="2">
         <v>32000</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="G18" s="1"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" t="s">
+      <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="1">
         <v>110</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="1">
         <v>100</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19" s="2">
         <v>11000</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H19" s="7"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="6"/>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1">
-      <c r="H24" s="4"/>
+      <c r="A24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="3"/>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" showErrorMessage="1" errorTitle="Invalid Product" error="Please select: Laptop, Phone, or Headphones" sqref="B2:B1000" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>"Laptop,Phone,Headphones"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showErrorMessage="1" errorTitle="Invalid Region" error="Please select: North, South, East, or West" sqref="F2:F1000" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>"North,South,East,West"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showErrorMessage="1" errorTitle="Invalid Month" error="Please select a valid month" sqref="A2:A1000" xr:uid="{00000000-0002-0000-0000-000002000000}">
+      <formula1>"January,February,March,April,May,June"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
@@ -1353,117 +1383,117 @@
   <dimension ref="B2:C16"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="2" max="2" width="22" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="18.600000000000001">
-      <c r="B2" s="8" t="s">
+    <row r="2" spans="2:3" ht="18.600000000000001" customHeight="1">
+      <c r="B2" s="7" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" spans="2:3">
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5" spans="2:3">
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="10">
         <f>SUM('Raw Data'!E2:E19)</f>
         <v>359500</v>
       </c>
     </row>
     <row r="6" spans="2:3">
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="12" t="str">
+      <c r="C6" s="11" t="str">
         <f>INDEX('Raw Data'!A2:A19,MATCH(MAX('Raw Data'!E2:E19),'Raw Data'!E2:E19,0))</f>
         <v>June</v>
       </c>
     </row>
     <row r="7" spans="2:3">
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="12" t="str">
+      <c r="C7" s="11" t="str">
         <f>INDEX('Raw Data'!B2:B19,MATCH(MAX('Raw Data'!E2:E19),'Raw Data'!E2:E19,0))</f>
         <v>Laptop</v>
       </c>
     </row>
     <row r="8" spans="2:3">
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="11">
         <f>SUM('Raw Data'!C2:C19)</f>
         <v>1090</v>
       </c>
     </row>
     <row r="10" spans="2:3">
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="8" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="11" spans="2:3">
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="10">
         <f>SUMIF('Raw Data'!A:A,B11,'Raw Data'!E:E)</f>
         <v>52000</v>
       </c>
     </row>
     <row r="12" spans="2:3">
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="10">
         <f>SUMIF('Raw Data'!A:A,B12,'Raw Data'!E:E)</f>
         <v>53000</v>
       </c>
     </row>
     <row r="13" spans="2:3">
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="10">
         <f>SUMIF('Raw Data'!A:A,B13,'Raw Data'!E:E)</f>
         <v>66000</v>
       </c>
     </row>
     <row r="14" spans="2:3">
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="10">
         <f>SUMIF('Raw Data'!A:A,B14,'Raw Data'!E:E)</f>
         <v>48000</v>
       </c>
     </row>
     <row r="15" spans="2:3">
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="10">
         <f>SUMIF('Raw Data'!A:A,B15,'Raw Data'!E:E)</f>
         <v>61500</v>
       </c>
     </row>
     <row r="16" spans="2:3">
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="10">
         <f>SUMIF('Raw Data'!A:A,B16,'Raw Data'!E:E)</f>
         <v>79000</v>
       </c>
